--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67647_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67647_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R31cb14ff469f4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R88696d4659cc41b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    348.9682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    240.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    295.2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    372.7337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    342.6761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    316.3481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    254.6952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    240.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.0006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    318.3192</x:v>
+        <x:v>    314.3860</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67647_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67647_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R88696d4659cc41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd712e2f091144a3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    516.0863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1730.9466</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    214.5826</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    190.3832</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    202.1177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    230.8094</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    277.0375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    300.9037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    310.4888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    372.7337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    244.8974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    280.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    404.5586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    651.3497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    320.2994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    271.7463</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    336.4652</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    428.3729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    266.5363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    310.4888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    433.2439</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    791.5153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    841.7721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    338.5265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    390.7029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    983.1015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1180.4286</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    196.8122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    213.1615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    226.2757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    263.1081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.0365</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    241.7036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    218.8998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    202.1177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    198.1250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    202.1177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    207.5674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    211.7495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    221.8231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    235.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    256.3598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    280.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    340.5968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    518.8239</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    849.0959</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    753.2678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    342.6761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    856.4558</x:v>
+        <x:v>    791.5153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    955.4166</x:v>
+        <x:v>    716.1114</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    841.7721</x:v>
+        <x:v>    805.6940</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1562.1134</x:v>
+        <x:v>    908.9849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1252.1486</x:v>
+        <x:v>   1154.1287</x:v>
       </x:c>
     </x:row>
     <x:row>
